--- a/templates/영종_상황판_표준시트_템플릿.xlsx
+++ b/templates/영종_상황판_표준시트_템플릿.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_CODE\01_영종\03_코덱스_영종\yeongjong_dashboard_app_v2\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_CODE\01_영종\03_코덱스_영종\yeongjong_dashboard_app_v2\yeongjong-dashboard\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A93142-DAC2-4ABE-837F-2C4A5C289467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D3200D-A238-40DA-91B8-159707059B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1940" yWindow="7320" windowWidth="21940" windowHeight="8610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="위험물업체" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,22 @@
     <author>인천소방본부_정보기획팀</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{7AB78039-E947-4D82-A50A-00059AB2CC76}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{FA462412-30A0-45FA-836C-038A94C3CB42}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>위도(Latitude, 가로선, 북/남 36~37범위)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{08099DD9-2592-4001-8FED-6F95AB4F09BD}">
       <text>
         <r>
           <rPr>
@@ -57,7 +72,17 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{0BF0C68A-D4D2-4326-90AA-79B1C1B62A15}">
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>인천소방본부_정보기획팀</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{273C93F1-D810-4F69-BE76-D189490C6206}">
       <text>
         <r>
           <rPr>
@@ -72,17 +97,7 @@
         </r>
       </text>
     </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>인천소방본부_정보기획팀</author>
-  </authors>
-  <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{F9C2DC7E-E060-4639-B983-5AB6BD7A1FD2}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{2048F98B-602A-455F-BCD0-8B79B9D3C298}">
       <text>
         <r>
           <rPr>
@@ -107,7 +122,17 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{4D380AD3-EFBF-4182-B5C6-7F3D3AC48174}">
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>인천소방본부_정보기획팀</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{96943F41-BDEF-436D-A0D8-F94581E6B846}">
       <text>
         <r>
           <rPr>
@@ -122,17 +147,7 @@
         </r>
       </text>
     </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>인천소방본부_정보기획팀</author>
-  </authors>
-  <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{878F278B-3774-49F0-80AD-4EA66C4C08C1}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{188B0CF8-B2A3-4BC4-970A-DA278EAD73F1}">
       <text>
         <r>
           <rPr>
@@ -157,27 +172,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{ABEFF858-7022-44B3-B9A0-986A15397ECC}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>위도(Latitude, 가로선, 북/남 36~37범위)</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="60">
   <si>
     <t>display_value</t>
   </si>
@@ -439,7 +439,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -454,6 +454,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -623,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12.1640625" customWidth="1"/>
@@ -651,10 +654,10 @@
         <v>49</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>50</v>
@@ -683,7 +686,7 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
+      <c r="B2" s="6"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -693,14 +696,12 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="4"/>
-      <c r="L2" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="2"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -710,14 +711,12 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="2"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -727,14 +726,12 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="4"/>
-      <c r="L4" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="2"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -744,14 +741,12 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="4"/>
-      <c r="L5" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="2"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -761,14 +756,12 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="4"/>
-      <c r="L6" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="2"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -778,27 +771,8 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="4"/>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="L7" s="2"/>
       <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -835,10 +809,10 @@
         <v>49</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -1078,10 +1052,10 @@
         <v>59</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>

--- a/templates/영종_상황판_표준시트_템플릿.xlsx
+++ b/templates/영종_상황판_표준시트_템플릿.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_CODE\01_영종\03_코덱스_영종\yeongjong_dashboard_app_v2\yeongjong-dashboard\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_CODE\01_영종\03_코덱스_영종\yeongjong_dashboard_app_v2\yeongjong-dashboard_ZIP배포용\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D3200D-A238-40DA-91B8-159707059B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A205F0D-57F9-4C7A-9B6D-572FACAE2876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1940" yWindow="7320" windowWidth="21940" windowHeight="8610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11680" yWindow="2750" windowWidth="15140" windowHeight="6160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="위험물업체" sheetId="1" r:id="rId1"/>
